--- a/Boolean_query_date_rage.xlsx
+++ b/Boolean_query_date_rage.xlsx
@@ -1,35 +1,149 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Search Period</t>
+  </si>
+  <si>
+    <t>Last Accessed</t>
+  </si>
+  <si>
+    <t>Results Found</t>
+  </si>
+  <si>
+    <t>ACM Digital Library</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/</t>
+  </si>
+  <si>
+    <t>Jan 2018 – Jul 2025</t>
+  </si>
+  <si>
+    <t>IEEE Xplore</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/Xplore/home.jsp</t>
+  </si>
+  <si>
+    <t>Web of Science</t>
+  </si>
+  <si>
+    <t>https://webofscience.clarivate.cn/wos/woscc/basic-search</t>
+  </si>
+  <si>
+    <t>Scopus</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/home#basic</t>
+  </si>
+  <si>
+    <t>ScienceDirect</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search</t>
+  </si>
+  <si>
+    <t>Springer</t>
+  </si>
+  <si>
+    <t>https://www.springer.com/gp</t>
+  </si>
+  <si>
+    <t>Boolean Query:</t>
+  </si>
+  <si>
+    <t>("adversarial attack" OR "adversarial example" OR "adversarial patch") AND ("physical" OR "real world") AND ("camouflage" OR "optical" OR "light" OR "illumination" OR "laser" OR "infrared" OR "camera" OR "sensor")</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0F1115"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0F1115"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000033"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.5"/>
+      <color rgb="FF000033"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -176,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,6 +299,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -370,12 +496,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -496,139 +674,175 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -689,6 +903,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,33 +1162,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="27.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="64" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="49.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45841</v>
+      </c>
+      <c r="E2" s="7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6">
+        <v>45841</v>
+      </c>
+      <c r="E3" s="7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6">
+        <v>45843</v>
+      </c>
+      <c r="E4" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>45844</v>
+      </c>
+      <c r="E5" s="7">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6">
+        <v>45848</v>
+      </c>
+      <c r="E6" s="7">
+        <v>152</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6">
+        <v>45848</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:5">
+      <c r="A8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" customHeight="1" spans="3:3">
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:3">
+      <c r="C10" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://dl.acm.org/" tooltip="https://dl.acm.org/}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://ieeexplore.ieee.org/Xplore/home.jsp" tooltip="https://ieeexplore.ieee.org/Xplore/home.jsp}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://webofscience.clarivate.cn/wos/woscc/basic-search" tooltip="https://webofscience.clarivate.cn/wos/woscc/basic-search}"/>
+    <hyperlink ref="B5" r:id="rId4" location="basic}" display="https://www.scopus.com/pages/home#basic"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.sciencedirect.com/search" tooltip="https://www.sciencedirect.com/search}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.springer.com/gp" tooltip="https://www.springer.com/gp}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
